--- a/data/trans_dic/IP04D$individual-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,39; 34,62</t>
+          <t>21,86; 34,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,8; 31,16</t>
+          <t>19,68; 31,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 24,82</t>
+          <t>11,07; 25,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,27; 45,51</t>
+          <t>32,61; 45,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,74; 36,48</t>
+          <t>22,91; 35,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,15; 33,67</t>
+          <t>16,76; 33,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,73; 38,22</t>
+          <t>29,03; 38,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,75; 31,36</t>
+          <t>22,6; 31,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 26,94</t>
+          <t>15,85; 27,32</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,04; 32,63</t>
+          <t>22,64; 32,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,0; 42,31</t>
+          <t>32,38; 42,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 22,56</t>
+          <t>12,44; 22,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,53; 32,07</t>
+          <t>22,69; 31,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,89; 33,33</t>
+          <t>24,27; 33,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 23,2</t>
+          <t>12,26; 22,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,28; 30,63</t>
+          <t>24,01; 30,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,55; 36,36</t>
+          <t>29,16; 36,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,89; 20,5</t>
+          <t>13,77; 20,59</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,18; 36,88</t>
+          <t>25,13; 36,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,26; 36,1</t>
+          <t>24,74; 35,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,61; 20,52</t>
+          <t>10,45; 20,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,53; 40,7</t>
+          <t>27,66; 40,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,21; 35,43</t>
+          <t>24,44; 35,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,53; 26,44</t>
+          <t>15,83; 26,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,15; 36,84</t>
+          <t>28,06; 36,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,17; 33,88</t>
+          <t>26,29; 34,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,37; 21,72</t>
+          <t>14,43; 21,71</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,23; 33,09</t>
+          <t>21,5; 33,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,88; 38,7</t>
+          <t>25,86; 38,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,14; 21,24</t>
+          <t>11,21; 21,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,33; 36,13</t>
+          <t>25,01; 36,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,68; 32,81</t>
+          <t>22,11; 34,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,5; 32,99</t>
+          <t>16,86; 32,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,83; 32,36</t>
+          <t>24,97; 32,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,96; 34,03</t>
+          <t>25,93; 34,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,46; 25,1</t>
+          <t>15,63; 25,34</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,48; 30,94</t>
+          <t>25,65; 31,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,96; 34,57</t>
+          <t>28,87; 34,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,62; 18,88</t>
+          <t>13,14; 18,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,13; 34,51</t>
+          <t>28,85; 34,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,08; 31,18</t>
+          <t>25,72; 31,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,69; 24,76</t>
+          <t>17,63; 25,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,0; 32,0</t>
+          <t>27,92; 31,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,25; 32,25</t>
+          <t>28,46; 32,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 21,11</t>
+          <t>16,44; 21,29</t>
         </is>
       </c>
     </row>
@@ -1180,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>40575</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33308</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9739</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56441</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35698</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15221</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97016</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>69006</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>24960</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>31575; 49139</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25909; 41207</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6365; 14768</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>47399; 66375</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28448; 43767</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10295; 20751</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>84144; 110663</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>57811; 81635</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>18855; 32501</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>64646</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77708</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27000</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>73252</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73713</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30864</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>137898</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>151421</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>57864</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>53487; 76053</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67492; 89569</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19815; 35310</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>60881; 85349</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>62142; 85744</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22285; 40578</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>121130; 155162</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>135441; 167894</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>46987; 70233</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>48225</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56011</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25608</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53346</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55402</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43611</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>101570</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>111413</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>69219</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>39272; 57554</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>46372; 66869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18163; 35236</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43854; 64118</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>45552; 65623</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>33496; 56829</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>88355; 115490</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>98291; 129193</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>55622; 83688</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>46463</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55718</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45085</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54982</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47226</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66619</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>101445</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>102944</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>111704</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>36843; 57888</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>44652; 66453</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30778; 57976</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45010; 65234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>38332; 58992</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>51493; 99690</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>87714; 115718</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>89732; 118866</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>90666; 146941</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>199908</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>222745</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>107431</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>156315</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>437929</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>434784</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>263747</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>181701; 221031</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>202173; 242461</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>87393; 123999</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>217052; 258778</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>190319; 232392</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>134069; 191362</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>407801; 466932</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>409889; 465742</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>234280; 303437</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$individual-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,86; 34,02</t>
+          <t>22,49; 34,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,68; 31,3</t>
+          <t>19,92; 31,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,07; 25,68</t>
+          <t>10,61; 25,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,61; 45,66</t>
+          <t>32,27; 45,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,91; 35,25</t>
+          <t>23,06; 36,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,76; 33,77</t>
+          <t>16,56; 34,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,03; 38,18</t>
+          <t>29,03; 37,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,6; 31,91</t>
+          <t>22,71; 31,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,85; 27,32</t>
+          <t>15,63; 27,89</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,64; 32,19</t>
+          <t>22,89; 32,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,38; 42,97</t>
+          <t>31,69; 42,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,44; 22,17</t>
+          <t>12,37; 22,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,69; 31,81</t>
+          <t>22,51; 31,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,27; 33,48</t>
+          <t>24,0; 33,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 22,31</t>
+          <t>12,21; 22,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,01; 30,75</t>
+          <t>23,96; 30,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,16; 36,14</t>
+          <t>29,49; 36,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,77; 20,59</t>
+          <t>13,6; 20,93</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,13; 36,83</t>
+          <t>25,07; 37,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,74; 35,67</t>
+          <t>24,74; 35,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,45; 20,26</t>
+          <t>10,36; 19,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,66; 40,43</t>
+          <t>27,39; 39,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,44; 35,21</t>
+          <t>24,89; 35,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,83; 26,86</t>
+          <t>15,59; 26,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,06; 36,68</t>
+          <t>28,13; 37,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,29; 34,56</t>
+          <t>25,57; 33,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,43; 21,71</t>
+          <t>14,83; 22,13</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,5; 33,79</t>
+          <t>21,37; 32,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,86; 38,49</t>
+          <t>26,67; 37,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,21; 21,12</t>
+          <t>11,29; 21,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,01; 36,25</t>
+          <t>25,32; 36,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,11; 34,03</t>
+          <t>22,02; 33,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,86; 32,63</t>
+          <t>15,89; 32,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,97; 32,94</t>
+          <t>24,92; 33,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,93; 34,35</t>
+          <t>25,9; 34,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,63; 25,34</t>
+          <t>15,35; 24,45</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,65; 31,21</t>
+          <t>25,4; 31,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,87; 34,63</t>
+          <t>29,0; 34,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,14; 18,64</t>
+          <t>13,43; 19,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,85; 34,4</t>
+          <t>28,9; 34,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,72; 31,4</t>
+          <t>26,14; 31,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,63; 25,17</t>
+          <t>17,7; 24,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,92; 31,97</t>
+          <t>28,01; 32,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,46; 32,34</t>
+          <t>28,13; 32,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,44; 21,29</t>
+          <t>16,32; 21,11</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31575; 49139</t>
+          <t>32489; 49222</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25909; 41207</t>
+          <t>26231; 41457</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6365; 14768</t>
+          <t>6102; 14411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47399; 66375</t>
+          <t>46913; 66632</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28448; 43767</t>
+          <t>28636; 44944</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10295; 20751</t>
+          <t>10173; 21205</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84144; 110663</t>
+          <t>84121; 109871</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57811; 81635</t>
+          <t>58089; 80019</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18855; 32501</t>
+          <t>18597; 33176</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53487; 76053</t>
+          <t>54071; 76673</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67492; 89569</t>
+          <t>66050; 89124</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19815; 35310</t>
+          <t>19711; 35845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60881; 85349</t>
+          <t>60393; 85823</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62142; 85744</t>
+          <t>61472; 84866</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22285; 40578</t>
+          <t>22207; 41048</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>121130; 155162</t>
+          <t>120892; 155428</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>135441; 167894</t>
+          <t>136971; 169372</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46987; 70233</t>
+          <t>46388; 71399</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39272; 57554</t>
+          <t>39169; 58033</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46372; 66869</t>
+          <t>46370; 66943</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18163; 35236</t>
+          <t>18020; 34453</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43854; 64118</t>
+          <t>43439; 63305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45552; 65623</t>
+          <t>46390; 66466</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33496; 56829</t>
+          <t>32973; 55031</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88355; 115490</t>
+          <t>88569; 116657</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>98291; 129193</t>
+          <t>95606; 125593</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55622; 83688</t>
+          <t>57158; 85314</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36843; 57888</t>
+          <t>36606; 55834</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44652; 66453</t>
+          <t>46041; 65577</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30778; 57976</t>
+          <t>30983; 59158</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45010; 65234</t>
+          <t>45568; 65609</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38332; 58992</t>
+          <t>38172; 57668</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51493; 99690</t>
+          <t>48532; 98148</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87714; 115718</t>
+          <t>87543; 116089</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89732; 118866</t>
+          <t>89619; 118438</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90666; 146941</t>
+          <t>89050; 141768</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>181701; 221031</t>
+          <t>179896; 219776</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202173; 242461</t>
+          <t>203027; 242223</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87393; 123999</t>
+          <t>89346; 126675</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217052; 258778</t>
+          <t>217360; 259166</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>190319; 232392</t>
+          <t>193406; 234009</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134069; 191362</t>
+          <t>134546; 189991</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>407801; 466932</t>
+          <t>409122; 467887</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>409889; 465742</t>
+          <t>405192; 463161</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>234280; 303437</t>
+          <t>232576; 300917</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$individual-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Edad-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción individual en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38,83%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28,75%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>28,09%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>25,3%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28,75%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,49; 34,07</t>
+          <t>32,27; 45,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,92; 31,49</t>
+          <t>22,74; 36,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 25,06</t>
+          <t>15,11; 31,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,27; 45,84</t>
+          <t>22,39; 34,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,06; 36,2</t>
+          <t>19,8; 31,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,56; 34,51</t>
+          <t>10,19; 24,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,03; 37,91</t>
+          <t>28,73; 38,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,71; 31,28</t>
+          <t>22,75; 31,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,63; 27,89</t>
+          <t>14,65; 25,78</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27,3%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>27,36%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>37,28%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27,3%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,89; 32,45</t>
+          <t>22,53; 32,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,69; 42,76</t>
+          <t>23,89; 33,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,37; 22,5</t>
+          <t>12,96; 23,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,51; 31,98</t>
+          <t>23,04; 32,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,0; 33,14</t>
+          <t>32,0; 42,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 22,57</t>
+          <t>12,88; 23,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,96; 30,8</t>
+          <t>24,28; 30,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,49; 36,46</t>
+          <t>29,55; 36,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,6; 20,93</t>
+          <t>14,29; 21,18</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33,64%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29,72%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>30,86%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>29,88%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14,73%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29,72%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,07; 37,14</t>
+          <t>27,53; 40,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,74; 35,71</t>
+          <t>24,21; 35,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 19,81</t>
+          <t>15,32; 26,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,39; 39,92</t>
+          <t>25,18; 36,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,89; 35,66</t>
+          <t>25,26; 36,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,59; 26,01</t>
+          <t>10,83; 20,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,13; 37,05</t>
+          <t>28,15; 36,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,57; 33,6</t>
+          <t>26,17; 33,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,83; 22,13</t>
+          <t>14,29; 21,56</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30,55%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21,84%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>27,12%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>32,27%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16,43%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30,55%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,37; 32,59</t>
+          <t>25,33; 36,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,67; 37,99</t>
+          <t>21,68; 32,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 21,55</t>
+          <t>17,01; 31,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,32; 36,46</t>
+          <t>21,23; 33,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,02; 33,26</t>
+          <t>26,88; 38,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,89; 32,13</t>
+          <t>14,32; 23,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,92; 33,05</t>
+          <t>24,83; 32,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,9; 34,23</t>
+          <t>25,96; 34,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,35; 24,45</t>
+          <t>16,82; 25,22</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>28,22%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>31,81%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,4; 31,03</t>
+          <t>29,13; 34,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,0; 34,59</t>
+          <t>26,08; 31,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,43; 19,04</t>
+          <t>17,68; 24,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,9; 34,45</t>
+          <t>25,48; 30,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,14; 31,62</t>
+          <t>28,96; 34,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,7; 24,99</t>
+          <t>14,76; 19,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,01; 32,04</t>
+          <t>28,0; 32,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,13; 32,16</t>
+          <t>28,25; 32,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 21,11</t>
+          <t>16,88; 21,28</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción individual en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>56441</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35698</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11628</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>40575</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>33308</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9739</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56441</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>35698</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15221</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24960</t>
+          <t>20491</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32489; 49222</t>
+          <t>46912; 66154</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26231; 41457</t>
+          <t>28229; 45295</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6102; 14411</t>
+          <t>7636; 15755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46913; 66632</t>
+          <t>32343; 50005</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28636; 44944</t>
+          <t>26063; 41026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10173; 21205</t>
+          <t>5307; 12897</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84121; 109871</t>
+          <t>83252; 110779</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58089; 80019</t>
+          <t>58199; 80228</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18597; 33176</t>
+          <t>15030; 26459</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>73252</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73713</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27706</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>64646</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>77708</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>27000</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73252</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73713</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>24915</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>57864</t>
+          <t>52621</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54071; 76673</t>
+          <t>60444; 86060</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66050; 89124</t>
+          <t>61182; 85362</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19711; 35845</t>
+          <t>20334; 37578</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60393; 85823</t>
+          <t>54435; 77082</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61472; 84866</t>
+          <t>66701; 88204</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22207; 41048</t>
+          <t>18739; 33546</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120892; 155428</t>
+          <t>122508; 154554</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>136971; 169372</t>
+          <t>137250; 168892</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46388; 71399</t>
+          <t>43214; 64053</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53346</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55402</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>40684</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>48225</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>56011</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25608</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>53346</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>55402</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43611</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69219</t>
+          <t>66909</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39169; 58033</t>
+          <t>43654; 64534</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46370; 66943</t>
+          <t>45119; 66035</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18020; 34453</t>
+          <t>30508; 52208</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43439; 63305</t>
+          <t>39349; 57623</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46390; 66466</t>
+          <t>47350; 67670</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32973; 55031</t>
+          <t>19009; 36420</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88569; 116657</t>
+          <t>88638; 115991</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95606; 125593</t>
+          <t>97824; 126641</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57158; 85314</t>
+          <t>53538; 80797</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54982</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47226</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>63902</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>46463</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>55718</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>45085</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54982</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>47226</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66619</t>
+          <t>46855</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>111704</t>
+          <t>110757</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36606; 55834</t>
+          <t>45581; 65024</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46041; 65577</t>
+          <t>37587; 56892</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30983; 59158</t>
+          <t>49789; 91226</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45568; 65609</t>
+          <t>36367; 56696</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38172; 57668</t>
+          <t>46402; 66818</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48532; 98148</t>
+          <t>36573; 58789</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87543; 116089</t>
+          <t>87227; 113686</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89619; 118438</t>
+          <t>89823; 117747</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89050; 141768</t>
+          <t>92174; 138209</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>154</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143920</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>199908</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>222745</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>107431</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>238021</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>212039</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>156315</t>
+          <t>106858</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>263747</t>
+          <t>250778</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>179896; 219776</t>
+          <t>219149; 259581</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>203027; 242223</t>
+          <t>193026; 230708</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89346; 126675</t>
+          <t>123615; 172157</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217360; 259166</t>
+          <t>180444; 219171</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>193406; 234009</t>
+          <t>202777; 242038</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134546; 189991</t>
+          <t>92798; 123777</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>409122; 467887</t>
+          <t>409018; 467293</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>405192; 463161</t>
+          <t>406858; 464447</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>232576; 300917</t>
+          <t>224131; 282524</t>
         </is>
       </c>
     </row>
